--- a/e_commerce_forms/002_profile_builder_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/002_profile_builder_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>create_profile</t>
+          <t>profile_field_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Create Profile</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What's your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tell us your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>select_profile_field</t>
+          <t>select_profile_field_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Profile Field</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Are you a team member?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>select_profile_field</t>
+          <t>select_profile_field_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Profile Field</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Can you select multiple options?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,38 +601,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your email address?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Your email address for contact purposes</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>select_profile_field_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Is this a public profile?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>select_profile_field_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Can you select multiple options again?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your favorite color?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tell us your favorite color</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your age?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Your age</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your height?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Your height in inches</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your date of birth?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Your date of birth</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your favorite time?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Your favorite time</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,43 +812,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_profile_field</t>
+          <t>profile_field_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select Profile Field</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your email?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Your email address</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_profile_field</t>
+          <t>profile_field_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Select Profile Field</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Your phone number</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is your favorite hobby?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tell us your favorite hobby</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is your favorite food?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tell us your favorite food</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>profile_field_11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What is your favorite animal?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tell us your favorite animal</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,202 +952,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>checkbox_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Checkbox 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>profile_field</t>
+          <t>radio_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Can you select single option?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Choose Yes or No</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>profile_field</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Profile Field</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1012,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1054,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1071,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1088,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1105,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1156,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_profile_field_choices</t>
+          <t>select_profile_field_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
